--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1107,36 +1107,43 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24791</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>148</v>
       </c>
       <c r="I12" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2025</v>
+        <v>20242025</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1145,66 +1152,838 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45527.6875</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>148</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>148</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>148</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>148</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>148</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>148</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>148</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45529.6875</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>148</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>148</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>148</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>148</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>148</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1484</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>45665.66666666666</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
         <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>148</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="H26" t="n">
+        <v>148</v>
+      </c>
+      <c r="I26" t="n">
         <v>1484</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K26" t="n">
         <v>2025</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>YT0e2vMU</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,43 +1231,36 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.5</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>23516</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>148</v>
       </c>
       <c r="I14" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>20242025</v>
+        <v>2025</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1276,49 +1269,49 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>super cup</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>148</v>
       </c>
       <c r="I15" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>20242025</v>
+        <v>2025</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1327,663 +1320,15 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>super cup</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>148</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>148</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>148</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45529.58333333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>12454</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>148</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45529.59375</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>148</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45529.6875</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>148</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45530.6875</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>148</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45531.58333333334</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>148</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45531.6875</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>14505</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>148</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>148</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1484</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>148</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1484</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>YT0e2vMU</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,36 +1231,43 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45528.5</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>148</v>
       </c>
       <c r="I14" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2025</v>
+        <v>20242025</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1269,66 +1276,470 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>YT0e2vMU</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>148</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>W8mj7MDD</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>148</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>148</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>148</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>148</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>148</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>148</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1484</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>4jDQxrbf</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>148</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="H22" t="n">
+        <v>148</v>
+      </c>
+      <c r="I22" t="n">
         <v>1484</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K22" t="n">
         <v>2025</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>YT0e2vMU</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -565,6 +635,48 @@
           <t>G8FL0ShI</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>151</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>154</v>
+      </c>
+      <c r="W2" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="X2" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>376</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>388</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -627,6 +739,34 @@
           <t>G8FL0ShI</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>183</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>233</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -685,6 +825,20 @@
           <t>YT0e2vMU</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -743,6 +897,20 @@
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -801,6 +969,20 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -863,6 +1045,20 @@
           <t>Mi0rXQg7</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -925,6 +1121,20 @@
           <t>69w4Rb2d</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -987,6 +1197,20 @@
           <t>IHv6nz80</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1045,6 +1269,20 @@
           <t>h8oAv4Ts</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1103,6 +1341,20 @@
           <t>QFfPdh1J</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1165,6 +1417,20 @@
           <t>zcgwCMgS</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1227,6 +1493,20 @@
           <t>vJbTeCGP</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1289,6 +1569,20 @@
           <t>W8mj7MDD</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1347,6 +1641,20 @@
           <t>G8FL0ShI</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1409,6 +1717,20 @@
           <t>dboeiWOt</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1467,6 +1789,20 @@
           <t>SKbpVP5K</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1521,6 +1857,20 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1579,6 +1929,20 @@
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1641,6 +2005,20 @@
           <t>SKbpVP5K</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1703,6 +2081,20 @@
           <t>69w4Rb2d</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1757,6 +2149,20 @@
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1819,6 +2225,20 @@
           <t>Mi0rXQg7</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -1881,6 +2301,20 @@
           <t>YT0e2vMU</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1943,6 +2377,20 @@
           <t>G8FL0ShI</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2001,6 +2449,20 @@
           <t>IHv6nz80</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2059,6 +2521,20 @@
           <t>zcgwCMgS</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2121,6 +2597,20 @@
           <t>QFfPdh1J</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2179,6 +2669,20 @@
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2241,112 +2745,20 @@
           <t>h8oAv4Ts</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>148</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1484</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>148</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1484</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23516</v>
+        <v>83186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,38 +630,42 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>28.33333333333333</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>174.3333333333333</v>
+        <v>182.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>220</v>
+        <v>411</v>
       </c>
       <c r="U2" t="n">
-        <v>11700000</v>
+        <v>267600000</v>
       </c>
       <c r="V2" t="n">
-        <v>220</v>
+        <v>423</v>
       </c>
       <c r="W2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="X2" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
@@ -673,44 +677,44 @@
         <v>69</v>
       </c>
       <c r="AB2" t="n">
-        <v>3400000</v>
+        <v>1400000</v>
       </c>
       <c r="AC2" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55926</v>
+        <v>12454</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -737,85 +741,75 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>177</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>170</v>
-      </c>
-      <c r="U3" t="n">
-        <v>172000000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>180</v>
-      </c>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>24.5</v>
+        <v>27</v>
       </c>
       <c r="X3" t="n">
-        <v>182.25</v>
+        <v>181.5</v>
       </c>
       <c r="Y3" t="n">
         <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>312</v>
+        <v>150</v>
       </c>
       <c r="AB3" t="n">
-        <v>85000000</v>
+        <v>13800000</v>
       </c>
       <c r="AC3" t="n">
-        <v>328</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45529.59375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>40000</v>
+        <v>19840</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -840,87 +834,73 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>178</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>27</v>
+      </c>
+      <c r="X4" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="Y4" t="n">
         <v>2</v>
       </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>74</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>75</v>
-      </c>
-      <c r="W4" t="n">
-        <v>20</v>
-      </c>
-      <c r="X4" t="n">
-        <v>182</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>74</v>
+        <v>216</v>
       </c>
       <c r="AB4" t="n">
-        <v>9500000</v>
+        <v>26650000</v>
       </c>
       <c r="AC4" t="n">
-        <v>85</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45529.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16500</v>
+        <v>70460</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -945,14 +925,10 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -963,26 +939,1500 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="X5" t="n">
-        <v>182</v>
+        <v>180.5</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>126</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>148</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>155</v>
+      </c>
+      <c r="U6" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>158</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>148</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>172</v>
+      </c>
+      <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="AA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>550000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>74</v>
-      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>69</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>81</v>
+      </c>
+      <c r="W7" t="n">
+        <v>28</v>
+      </c>
+      <c r="X7" t="n">
+        <v>184</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>78</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>148</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>133</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>152</v>
+      </c>
+      <c r="W8" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>331</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>241500000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>148</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>148</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>148</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>148</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45533.6875</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>148</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55926</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>148</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>148</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45535.59375</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>148</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>148</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>148</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>148</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>148</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>148</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45536.59375</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>148</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45536.6875</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>148</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5</v>
+        <v>45530.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83186</v>
+        <v>23000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,89 +632,75 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>zcgwCMgS</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q2" t="n">
-        <v>182.4</v>
+        <v>182.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>411</v>
+        <v>155</v>
       </c>
       <c r="U2" t="n">
-        <v>267600000</v>
+        <v>31000000</v>
       </c>
       <c r="V2" t="n">
-        <v>423</v>
-      </c>
-      <c r="W2" t="n">
-        <v>28</v>
-      </c>
-      <c r="X2" t="n">
-        <v>174</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>69</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>69</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.58333333334</v>
+        <v>45531.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12454</v>
+        <v>26020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -741,75 +727,75 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>YT0e2vMU</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>13800000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>150</v>
-      </c>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>172</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>69</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>81</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.59375</v>
+        <v>45531.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19840</v>
+        <v>14505</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -834,73 +820,91 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>133</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>152</v>
+      </c>
       <c r="W4" t="n">
-        <v>27</v>
+        <v>22.75</v>
       </c>
       <c r="X4" t="n">
-        <v>181.6666666666667</v>
+        <v>179.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>216</v>
+        <v>331</v>
       </c>
       <c r="AB4" t="n">
-        <v>26650000</v>
+        <v>241500000</v>
       </c>
       <c r="AC4" t="n">
-        <v>230</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70460</v>
+        <v>53331</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -928,65 +932,84 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>312</v>
+      </c>
+      <c r="U5" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>328</v>
+      </c>
       <c r="W5" t="n">
-        <v>19.5</v>
+        <v>26.4</v>
       </c>
       <c r="X5" t="n">
-        <v>180.5</v>
+        <v>179.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>126</v>
+        <v>376</v>
       </c>
       <c r="AB5" t="n">
-        <v>2400000</v>
+        <v>47000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>156</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45530.6875</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23000</v>
+        <v>27618</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1013,34 +1036,34 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.5</v>
+        <v>174</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="U6" t="n">
-        <v>31000000</v>
+        <v>1400000</v>
       </c>
       <c r="V6" t="n">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1053,30 +1076,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45531.58333333334</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45532.6875</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>26020</v>
+        <v>70460</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1101,42 +1129,38 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="U7" t="n">
-        <v>3400000</v>
+        <v>27500000</v>
       </c>
       <c r="V7" t="n">
         <v>81</v>
       </c>
       <c r="W7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X7" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="Y7" t="n">
         <v>2</v>
@@ -1145,42 +1169,47 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AB7" t="n">
-        <v>14000000</v>
+        <v>4900000</v>
       </c>
       <c r="AC7" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45531.6875</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45532.6875</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14505</v>
+        <v>40000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1205,86 +1234,83 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>182.5</v>
+        <v>178.25</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>133</v>
+        <v>305</v>
       </c>
       <c r="U8" t="n">
-        <v>4750000</v>
+        <v>53500000</v>
       </c>
       <c r="V8" t="n">
-        <v>152</v>
+        <v>327</v>
       </c>
       <c r="W8" t="n">
-        <v>22.75</v>
+        <v>31</v>
       </c>
       <c r="X8" t="n">
-        <v>179.75</v>
+        <v>180</v>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>331</v>
+        <v>73</v>
       </c>
       <c r="AB8" t="n">
-        <v>241500000</v>
+        <v>2100000</v>
       </c>
       <c r="AC8" t="n">
-        <v>353</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45532.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53331</v>
+        <v>14624</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1309,12 +1335,12 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -1333,30 +1359,35 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45532.58333333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45533.6875</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27618</v>
+        <v>32392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1383,12 +1414,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1409,30 +1440,30 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.5</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70460</v>
+        <v>55926</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1457,10 +1488,14 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1481,30 +1516,30 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>40000</v>
+        <v>53331</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1549,30 +1584,30 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45535.59375</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14624</v>
+        <v>40000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1599,10 +1634,14 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1621,30 +1660,30 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45535.6875</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>32392</v>
+        <v>12454</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1671,12 +1710,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>YT0e2vMU</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1697,30 +1736,30 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45535.5</v>
+        <v>45535.6875</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>55926</v>
+        <v>49430</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1747,12 +1786,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1773,30 +1812,30 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53331</v>
+        <v>19840</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1822,7 +1861,11 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1841,30 +1884,30 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.5</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40000</v>
+        <v>23516</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1889,14 +1932,10 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>zcgwCMgS</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1917,30 +1956,30 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12454</v>
+        <v>42714</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1967,12 +2006,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1993,30 +2032,30 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.59375</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49430</v>
+        <v>16500</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2043,14 +2082,10 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -2069,30 +2104,30 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.6875</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>19840</v>
+        <v>83186</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2117,10 +2152,14 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2138,302 +2177,6 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>148</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>148</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>148</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>148</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23000</v>
+        <v>53331</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,77 +630,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>G8FL0ShI</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q2" t="n">
-        <v>182.5</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="U2" t="n">
-        <v>31000000</v>
+        <v>81500000</v>
       </c>
       <c r="V2" t="n">
-        <v>158</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+        <v>247</v>
+      </c>
+      <c r="W2" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>182</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>37200000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45531.58333333334</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26020</v>
+        <v>27618</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -727,19 +737,19 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -751,10 +761,10 @@
         <v>69</v>
       </c>
       <c r="U3" t="n">
-        <v>3400000</v>
+        <v>1400000</v>
       </c>
       <c r="V3" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -767,35 +777,35 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45531.6875</v>
+        <v>45532.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
+          <t xml:space="preserve">metropolitano stadium
   madrid </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14505</v>
+        <v>70460</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -820,91 +830,73 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="R4" t="n">
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>26</v>
+      </c>
+      <c r="X4" t="n">
+        <v>178</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
-        <v>2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>133</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4750000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>152</v>
-      </c>
-      <c r="W4" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="X4" t="n">
-        <v>179.75</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
       <c r="AA4" t="n">
-        <v>331</v>
+        <v>74</v>
       </c>
       <c r="AB4" t="n">
-        <v>241500000</v>
+        <v>4900000</v>
       </c>
       <c r="AC4" t="n">
-        <v>353</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45532.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53331</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -930,86 +922,82 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>24.5</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="n">
-        <v>182.25</v>
+        <v>182</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>312</v>
+        <v>74</v>
       </c>
       <c r="U5" t="n">
-        <v>85000000</v>
+        <v>9500000</v>
       </c>
       <c r="V5" t="n">
-        <v>328</v>
+        <v>85</v>
       </c>
       <c r="W5" t="n">
-        <v>26.4</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>179.4</v>
+        <v>180</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>376</v>
+        <v>73</v>
       </c>
       <c r="AB5" t="n">
-        <v>47000000</v>
+        <v>2100000</v>
       </c>
       <c r="AC5" t="n">
-        <v>388</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45533.58333333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27618</v>
+        <v>14624</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1036,75 +1024,85 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>174</v>
+        <v>180.5</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>126</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>156</v>
+      </c>
+      <c r="W6" t="n">
+        <v>23</v>
+      </c>
+      <c r="X6" t="n">
+        <v>179</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
-        <v>69</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>69</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>138</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45533.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70460</v>
+        <v>32392</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1129,7 +1127,11 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
@@ -1139,77 +1141,72 @@
         <v>27</v>
       </c>
       <c r="Q7" t="n">
-        <v>171</v>
+        <v>181.5</v>
       </c>
       <c r="R7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>150</v>
+      </c>
+      <c r="U7" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>150</v>
+      </c>
+      <c r="W7" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="X7" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="Z7" t="n">
         <v>3</v>
       </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>81</v>
-      </c>
-      <c r="U7" t="n">
-        <v>27500000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>81</v>
-      </c>
-      <c r="W7" t="n">
-        <v>26</v>
-      </c>
-      <c r="X7" t="n">
-        <v>178</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
       <c r="AA7" t="n">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="AB7" t="n">
-        <v>4900000</v>
+        <v>237000000</v>
       </c>
       <c r="AC7" t="n">
-        <v>75</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45532.6875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
+        <v>45535.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>40000</v>
+        <v>55926</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1234,83 +1231,58 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>178.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>305</v>
-      </c>
-      <c r="U8" t="n">
-        <v>53500000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>327</v>
-      </c>
-      <c r="W8" t="n">
-        <v>31</v>
-      </c>
-      <c r="X8" t="n">
-        <v>180</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>73</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>73</v>
-      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45533.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">maeso f 
-  esp </t>
-        </is>
-      </c>
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>14624</v>
+        <v>53331</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1335,11 +1307,7 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1359,35 +1327,30 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45533.6875</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
+        <v>45535.59375</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32392</v>
+        <v>40000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1414,12 +1377,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1440,30 +1403,30 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5</v>
+        <v>45535.6875</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>55926</v>
+        <v>12454</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1490,12 +1453,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>YT0e2vMU</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1516,30 +1479,30 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45535.6875</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53331</v>
+        <v>49430</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1564,8 +1527,16 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1584,30 +1555,30 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.5</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>40000</v>
+        <v>19840</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1632,14 +1603,10 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1660,30 +1627,30 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.5</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12454</v>
+        <v>23516</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1708,14 +1675,10 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>zcgwCMgS</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1736,30 +1699,30 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49430</v>
+        <v>42714</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1786,12 +1749,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1812,30 +1775,30 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.59375</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19840</v>
+        <v>16500</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1860,12 +1823,12 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1884,30 +1847,30 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.6875</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>23516</v>
+        <v>83186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1932,10 +1895,14 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1953,230 +1920,6 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>148</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>148</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>148</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53331</v>
+        <v>55926</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,87 +630,91 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.6666666666667</v>
+        <v>181.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.666666666666667</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>242</v>
+        <v>417</v>
       </c>
       <c r="U2" t="n">
-        <v>81500000</v>
+        <v>334500000</v>
       </c>
       <c r="V2" t="n">
-        <v>247</v>
+        <v>444</v>
       </c>
       <c r="W2" t="n">
-        <v>28.66666666666667</v>
+        <v>28</v>
       </c>
       <c r="X2" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>230</v>
+        <v>69</v>
       </c>
       <c r="AB2" t="n">
-        <v>37200000</v>
+        <v>1400000</v>
       </c>
       <c r="AC2" t="n">
-        <v>233</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27618</v>
+        <v>53331</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -735,36 +739,28 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>174</v>
+        <v>182.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="U3" t="n">
-        <v>1400000</v>
+        <v>68000000</v>
       </c>
       <c r="V3" t="n">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -777,35 +773,35 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.59375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70460</v>
+        <v>40000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -830,73 +826,91 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>184</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>146</v>
+      </c>
+      <c r="U4" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>147</v>
+      </c>
       <c r="W4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="X4" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>550000</v>
+      </c>
+      <c r="AC4" t="n">
         <v>74</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>12454</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -921,34 +935,28 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>182</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>74</v>
-      </c>
-      <c r="U5" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>85</v>
-      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="X5" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
@@ -957,47 +965,47 @@
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="AB5" t="n">
-        <v>2100000</v>
+        <v>3400000</v>
       </c>
       <c r="AC5" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45535.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14624</v>
+        <v>49430</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1024,85 +1032,89 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
       <c r="P6" t="n">
-        <v>19.5</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="Q6" t="n">
-        <v>180.5</v>
+        <v>182</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>126</v>
+        <v>230</v>
       </c>
       <c r="U6" t="n">
-        <v>2400000</v>
+        <v>37200000</v>
       </c>
       <c r="V6" t="n">
-        <v>156</v>
+        <v>233</v>
       </c>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="X6" t="n">
-        <v>179</v>
+        <v>182.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
         <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="AB6" t="n">
-        <v>7200000</v>
+        <v>31000000</v>
       </c>
       <c r="AC6" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45536.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32392</v>
+        <v>19840</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1127,86 +1139,73 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>IHv6nz80</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
         <v>27</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="X7" t="n">
         <v>181.5</v>
       </c>
-      <c r="R7" t="n">
+      <c r="Y7" t="n">
         <v>1.5</v>
       </c>
-      <c r="S7" t="n">
+      <c r="Z7" t="n">
         <v>2</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AA7" t="n">
         <v>150</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AB7" t="n">
         <v>13800000</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AC7" t="n">
         <v>150</v>
-      </c>
-      <c r="W7" t="n">
-        <v>23.66666666666667</v>
-      </c>
-      <c r="X7" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>256</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>237000000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45536.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55926</v>
+        <v>23516</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1231,58 +1230,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>179</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>138</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>150</v>
+      </c>
+      <c r="W8" t="n">
+        <v>27</v>
+      </c>
+      <c r="X8" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>73</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53331</v>
+        <v>42714</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1307,50 +1335,91 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>184</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>80</v>
+      </c>
+      <c r="U9" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>80</v>
+      </c>
+      <c r="W9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>126</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.59375</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45536.59375</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>40000</v>
+        <v>16500</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1377,14 +1446,10 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
           <t>Mi0rXQg7</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1392,41 +1457,60 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>23</v>
+      </c>
+      <c r="X10" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>157</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>168</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.6875</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>45536.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12454</v>
+        <v>83186</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1453,472 +1537,56 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45535.6875</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>148</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>148</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>148</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
           <t>h8oAv4Ts</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>148</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>148</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>148</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>256</v>
+      </c>
+      <c r="U11" t="n">
+        <v>237000000</v>
+      </c>
+      <c r="V11" t="n">
+        <v>267</v>
+      </c>
+      <c r="W11" t="n">
+        <v>25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>135</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5150000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>149</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>55926</v>
+        <v>19840</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,91 +630,73 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>417</v>
-      </c>
-      <c r="U2" t="n">
-        <v>334500000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>444</v>
-      </c>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X2" t="n">
-        <v>174</v>
+        <v>181.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>1400000</v>
+        <v>13800000</v>
       </c>
       <c r="AC2" t="n">
-        <v>69</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53331</v>
+        <v>23516</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -740,68 +722,86 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
       <c r="P3" t="n">
-        <v>27.5</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>182.5</v>
+        <v>179</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="U3" t="n">
-        <v>68000000</v>
+        <v>7200000</v>
       </c>
       <c r="V3" t="n">
-        <v>166</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="W3" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>294</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>40000</v>
+        <v>42714</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -828,89 +828,89 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>184</v>
+        <v>185.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="U4" t="n">
-        <v>6400000</v>
+        <v>42000000</v>
       </c>
       <c r="V4" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="W4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="X4" t="n">
-        <v>182</v>
+        <v>180.5</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="AB4" t="n">
-        <v>550000</v>
+        <v>2400000</v>
       </c>
       <c r="AC4" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.59375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12454</v>
+        <v>16500</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -937,14 +937,10 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -953,59 +949,59 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>172</v>
+        <v>181.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="AB5" t="n">
-        <v>3400000</v>
+        <v>49000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>81</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49430</v>
+        <v>83186</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1032,40 +1028,40 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>28.66666666666667</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="Q6" t="n">
-        <v>182</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="R6" t="n">
-        <v>1.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="U6" t="n">
-        <v>37200000</v>
+        <v>237000000</v>
       </c>
       <c r="V6" t="n">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="W6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X6" t="n">
-        <v>182.5</v>
+        <v>184.5</v>
       </c>
       <c r="Y6" t="n">
         <v>1.5</v>
@@ -1074,517 +1070,12 @@
         <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="AB6" t="n">
-        <v>31000000</v>
+        <v>5150000</v>
       </c>
       <c r="AC6" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>148</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="n">
-        <v>27</v>
-      </c>
-      <c r="X7" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>13800000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>148</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>179</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>138</v>
-      </c>
-      <c r="U8" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>150</v>
-      </c>
-      <c r="W8" t="n">
-        <v>27</v>
-      </c>
-      <c r="X8" t="n">
-        <v>180</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>73</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>148</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>184</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>80</v>
-      </c>
-      <c r="U9" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>80</v>
-      </c>
-      <c r="W9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>126</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>148</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>157</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>49000000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>148</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>23.66666666666667</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>256</v>
-      </c>
-      <c r="U11" t="n">
-        <v>237000000</v>
-      </c>
-      <c r="V11" t="n">
-        <v>267</v>
-      </c>
-      <c r="W11" t="n">
-        <v>25</v>
-      </c>
-      <c r="X11" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>135</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5150000</v>
-      </c>
-      <c r="AC11" t="n">
         <v>149</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,109 +503,34 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YeqTho8m</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
+        <v>45548.66666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19840</v>
+        <v>60721</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,73 +555,44 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>27</v>
-      </c>
-      <c r="X2" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13800000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>150</v>
+          <t>dboeiWOt</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>08zpk37C</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
+        <v>45549.375</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23516</v>
+        <v>26020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -721,87 +617,44 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>179</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>138</v>
-      </c>
-      <c r="U3" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>150</v>
-      </c>
-      <c r="W3" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>176.75</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>294</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>300</v>
+          <t>G8FL0ShI</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
+        <v>45549.46875</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42714</v>
+        <v>40000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -828,89 +681,38 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>160</v>
-      </c>
-      <c r="U4" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>160</v>
-      </c>
-      <c r="W4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>126</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>156</v>
-      </c>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>8EcB5Oig</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
+        <v>45549.5625</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16500</v>
+        <v>42714</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -937,71 +739,42 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>Mi0rXQg7</t>
         </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>23</v>
-      </c>
-      <c r="X5" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>157</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>49000000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>168</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>jckS1tiI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>83186</v>
+        <v>40000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1026,58 +799,310 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>SKbpVP5K</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>23.66666666666667</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>256</v>
-      </c>
-      <c r="U6" t="n">
-        <v>237000000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>267</v>
-      </c>
-      <c r="W6" t="n">
-        <v>25</v>
-      </c>
-      <c r="X6" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>135</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5150000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>149</v>
-      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>148</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.46875</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>148</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.5625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>148</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>148</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45551.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>148</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,6 +1104,962 @@
       </c>
       <c r="O11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45552.58333333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>26020</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>148</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45553.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45554.58333333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>148</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45555.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>148</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>148</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.46875</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>148</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>148</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>148</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.375</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coliseum
+  getafe </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>148</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45557.46875</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>148</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45557.5625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>148</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45557.66666666666</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>148</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>60721</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>148</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>148</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>148</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>148</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,35 +567,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27618</v>
+        <v>24791</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -622,83 +622,83 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>zcgwCMgS</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>27</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>181</v>
+        <v>177.6666666666667</v>
       </c>
       <c r="R2" t="n">
-        <v>69.66666666666667</v>
+        <v>74.33333333333333</v>
       </c>
       <c r="S2" t="n">
-        <v>9000</v>
+        <v>19666.66666666667</v>
       </c>
       <c r="T2" t="n">
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="V2" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="W2" t="n">
-        <v>182</v>
+        <v>180.5</v>
       </c>
       <c r="X2" t="n">
-        <v>74.8</v>
+        <v>63</v>
       </c>
       <c r="Y2" t="n">
-        <v>23200</v>
+        <v>3500</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>374</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.375</v>
+        <v>45564.46875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16500</v>
+        <v>53331</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -723,57 +723,81 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>185</v>
+      </c>
+      <c r="R3" t="n">
+        <v>80</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30750</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>320</v>
+      </c>
+      <c r="V3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>78.66666666666667</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>38666.66666666666</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.46875</v>
+        <v>45564.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14505</v>
+        <v>60721</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -800,83 +824,83 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>30.66666666666667</v>
       </c>
       <c r="Q4" t="n">
-        <v>177</v>
+        <v>178.6666666666667</v>
       </c>
       <c r="R4" t="n">
-        <v>69</v>
+        <v>79.66666666666667</v>
       </c>
       <c r="S4" t="n">
-        <v>11000</v>
+        <v>28000</v>
       </c>
       <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>239</v>
+      </c>
+      <c r="V4" t="n">
+        <v>29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2</v>
       </c>
-      <c r="U4" t="n">
-        <v>138</v>
-      </c>
-      <c r="V4" t="n">
-        <v>26</v>
-      </c>
-      <c r="W4" t="n">
-        <v>180</v>
-      </c>
-      <c r="X4" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>7000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.5625</v>
+        <v>45564.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>70460</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -904,78 +928,78 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>25.5</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="n">
-        <v>178.5</v>
+        <v>178</v>
       </c>
       <c r="R5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S5" t="n">
-        <v>27500</v>
+        <v>51000</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="V5" t="n">
-        <v>28</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="W5" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="X5" t="n">
-        <v>76.75</v>
+        <v>84</v>
       </c>
       <c r="Y5" t="n">
-        <v>30250</v>
+        <v>171666.6666666667</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>307</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23516</v>
+        <v>23000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1000,451 +1024,51 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>20</v>
+        <v>25.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>179</v>
+        <v>185.25</v>
       </c>
       <c r="R6" t="n">
-        <v>63</v>
+        <v>75.5</v>
       </c>
       <c r="S6" t="n">
-        <v>4000</v>
+        <v>30750</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>63</v>
+        <v>302</v>
       </c>
       <c r="V6" t="n">
-        <v>25.16666666666667</v>
+        <v>24.5</v>
       </c>
       <c r="W6" t="n">
-        <v>183</v>
+        <v>183.5</v>
       </c>
       <c r="X6" t="n">
-        <v>85.16666666666667</v>
+        <v>72.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>153500</v>
+        <v>54500</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45564.375</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>148</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>181</v>
-      </c>
-      <c r="R7" t="n">
-        <v>74</v>
-      </c>
-      <c r="S7" t="n">
-        <v>17500</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>148</v>
-      </c>
-      <c r="V7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>63</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3500</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.46875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>148</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>190</v>
-      </c>
-      <c r="R8" t="n">
-        <v>85</v>
-      </c>
-      <c r="S8" t="n">
-        <v>38000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>85</v>
-      </c>
-      <c r="V8" t="n">
-        <v>27</v>
-      </c>
-      <c r="W8" t="n">
-        <v>184.3333333333333</v>
-      </c>
-      <c r="X8" t="n">
-        <v>78.66666666666667</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>38666.66666666666</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.5625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>60721</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>148</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>30.66666666666667</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>178.6666666666667</v>
-      </c>
-      <c r="R9" t="n">
-        <v>79.66666666666667</v>
-      </c>
-      <c r="S9" t="n">
-        <v>28000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>239</v>
-      </c>
-      <c r="V9" t="n">
-        <v>26</v>
-      </c>
-      <c r="W9" t="n">
-        <v>178</v>
-      </c>
-      <c r="X9" t="n">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.66666666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>148</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>178</v>
-      </c>
-      <c r="R10" t="n">
-        <v>79</v>
-      </c>
-      <c r="S10" t="n">
-        <v>51000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>79</v>
-      </c>
-      <c r="V10" t="n">
-        <v>26</v>
-      </c>
-      <c r="W10" t="n">
-        <v>177.75</v>
-      </c>
-      <c r="X10" t="n">
-        <v>84.25</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>178750</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>337</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,42 +495,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_home</t>
+          <t>sum_wage_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_home</t>
+          <t>sum_value_player_miss_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rep_player_miss_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -545,57 +545,67 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.375</v>
+        <v>45569.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24791</v>
+        <v>12454</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -620,85 +630,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
+      <c r="N2" t="n">
+        <v>22</v>
+      </c>
+      <c r="O2" t="n">
+        <v>180</v>
       </c>
       <c r="P2" t="n">
-        <v>26.33333333333333</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>177.6666666666667</v>
+        <v>64</v>
       </c>
       <c r="R2" t="n">
-        <v>74.33333333333333</v>
+        <v>20000</v>
       </c>
       <c r="S2" t="n">
-        <v>19666.66666666667</v>
+        <v>1300000</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="U2" t="n">
-        <v>223</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="W2" t="n">
-        <v>180.5</v>
+        <v>181</v>
       </c>
       <c r="X2" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>3500</v>
+        <v>305</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>143000</v>
       </c>
       <c r="AA2" t="n">
-        <v>126</v>
+        <v>51400000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>317</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.46875</v>
+        <v>45570.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53331</v>
+        <v>40000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -723,81 +735,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
+      <c r="N3" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="O3" t="n">
+        <v>181.6666666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="R3" t="n">
-        <v>80</v>
+        <v>62000</v>
       </c>
       <c r="S3" t="n">
-        <v>30750</v>
+        <v>19000000</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>226</v>
       </c>
       <c r="U3" t="n">
-        <v>320</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>27</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="W3" t="n">
         <v>184.3333333333333</v>
       </c>
       <c r="X3" t="n">
-        <v>78.66666666666667</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>38666.66666666666</v>
+        <v>222</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>82000</v>
       </c>
       <c r="AA3" t="n">
+        <v>27200000</v>
+      </c>
+      <c r="AB3" t="n">
         <v>236</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>40FWnYcm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5625</v>
+        <v>45570.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60721</v>
+        <v>16500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -822,85 +840,55 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>30.66666666666667</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>178.6666666666667</v>
-      </c>
-      <c r="R4" t="n">
-        <v>79.66666666666667</v>
-      </c>
-      <c r="S4" t="n">
-        <v>28000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>239</v>
-      </c>
-      <c r="V4" t="n">
-        <v>29</v>
-      </c>
-      <c r="W4" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>73</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>9000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>146</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.66666666666</v>
+        <v>45570.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70460</v>
+        <v>32392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -925,81 +913,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
+      <c r="N5" t="n">
+        <v>24</v>
+      </c>
+      <c r="O5" t="n">
+        <v>178</v>
       </c>
       <c r="P5" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="R5" t="n">
-        <v>79</v>
+        <v>16000</v>
       </c>
       <c r="S5" t="n">
-        <v>51000</v>
+        <v>3500000</v>
       </c>
       <c r="T5" t="n">
+        <v>77</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>79</v>
-      </c>
       <c r="V5" t="n">
-        <v>24.33333333333333</v>
+        <v>27</v>
       </c>
       <c r="W5" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="X5" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="n">
-        <v>171666.6666666667</v>
+        <v>141</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>39000</v>
       </c>
       <c r="AA5" t="n">
-        <v>252</v>
+        <v>4300000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>145</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45565.66666666666</v>
+        <v>45570.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23000</v>
+        <v>27618</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1024,52 +1018,767 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
+      <c r="N6" t="n">
+        <v>26</v>
+      </c>
+      <c r="O6" t="n">
+        <v>180.5</v>
       </c>
       <c r="P6" t="n">
-        <v>25.25</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>185.25</v>
+        <v>139</v>
       </c>
       <c r="R6" t="n">
-        <v>75.5</v>
+        <v>39000</v>
       </c>
       <c r="S6" t="n">
-        <v>30750</v>
+        <v>3600000</v>
       </c>
       <c r="T6" t="n">
+        <v>144</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>26</v>
+      </c>
+      <c r="W6" t="n">
+        <v>176</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>208</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>11950000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>225</v>
+      </c>
+      <c r="AC6" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>302</v>
-      </c>
-      <c r="V6" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>54500</v>
-      </c>
-      <c r="Z6" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>83186</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>148</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>185</v>
+      </c>
+      <c r="P7" t="n">
         <v>2</v>
       </c>
-      <c r="AA6" t="n">
-        <v>145</v>
-      </c>
+      <c r="Q7" t="n">
+        <v>171</v>
+      </c>
+      <c r="R7" t="n">
+        <v>380000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>94500000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>175</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" t="n">
+        <v>29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>316</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>181000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>73000000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>319</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>148</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>368</v>
+      </c>
+      <c r="R8" t="n">
+        <v>210000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>63900000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>399</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="W8" t="n">
+        <v>186.3333333333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>244</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>96000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>254</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.46875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>148</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>255</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>405000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>158000000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>264</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>42714</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>148</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>27</v>
+      </c>
+      <c r="O10" t="n">
+        <v>184</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>78</v>
+      </c>
+      <c r="R10" t="n">
+        <v>33000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>79</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>31.66666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>178.6666666666667</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>239</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>106000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>45500000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>239</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>148</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>154</v>
+      </c>
+      <c r="R11" t="n">
+        <v>67000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="T11" t="n">
+        <v>165</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>162</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>146000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>46500000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>165</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45583.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>19840</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>148</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53331</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.46875</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>148</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.66666666666</v>
+        <v>45571.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12454</v>
+        <v>14624</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -631,49 +631,49 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>26.4</v>
       </c>
       <c r="O2" t="n">
-        <v>180</v>
+        <v>180.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>64</v>
+        <v>368</v>
       </c>
       <c r="R2" t="n">
-        <v>20000</v>
+        <v>210000</v>
       </c>
       <c r="S2" t="n">
-        <v>1300000</v>
+        <v>63900000</v>
       </c>
       <c r="T2" t="n">
-        <v>75</v>
+        <v>399</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V2" t="n">
-        <v>26</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="W2" t="n">
-        <v>181</v>
+        <v>186.3333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="n">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="Z2" t="n">
-        <v>143000</v>
+        <v>96000</v>
       </c>
       <c r="AA2" t="n">
-        <v>51400000</v>
+        <v>102000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>317</v>
+        <v>254</v>
       </c>
       <c r="AC2" t="n">
         <v>7</v>
@@ -682,35 +682,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.375</v>
+        <v>45571.46875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40000</v>
+        <v>19840</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -735,87 +735,71 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>28.66666666666667</v>
-      </c>
-      <c r="O3" t="n">
-        <v>181.6666666666667</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>225</v>
-      </c>
-      <c r="R3" t="n">
-        <v>62000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>226</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>25.66666666666667</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="W3" t="n">
-        <v>184.3333333333333</v>
+        <v>182.3333333333333</v>
       </c>
       <c r="X3" t="n">
         <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="Z3" t="n">
-        <v>82000</v>
+        <v>405000</v>
       </c>
       <c r="AA3" t="n">
-        <v>27200000</v>
+        <v>158000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="AC3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.46875</v>
+        <v>45571.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16500</v>
+        <v>42714</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -840,55 +824,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O4" t="n">
+        <v>184</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>78</v>
+      </c>
+      <c r="R4" t="n">
+        <v>33000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>79</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>31.66666666666667</v>
+      </c>
+      <c r="W4" t="n">
+        <v>178.6666666666667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>239</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>106000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>45500000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>239</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45571.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>32392</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -914,86 +930,81 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>26.5</v>
       </c>
       <c r="O5" t="n">
-        <v>178</v>
+        <v>178.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="R5" t="n">
-        <v>16000</v>
+        <v>67000</v>
       </c>
       <c r="S5" t="n">
-        <v>3500000</v>
+        <v>24000000</v>
       </c>
       <c r="T5" t="n">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>27</v>
+        <v>30.5</v>
       </c>
       <c r="W5" t="n">
-        <v>182</v>
+        <v>182.5</v>
       </c>
       <c r="X5" t="n">
         <v>2</v>
       </c>
       <c r="Y5" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="Z5" t="n">
-        <v>39000</v>
+        <v>146000</v>
       </c>
       <c r="AA5" t="n">
-        <v>4300000</v>
+        <v>46500000</v>
       </c>
       <c r="AB5" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuertes p 
-  esp </t>
-        </is>
-      </c>
+        <v>45583.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27618</v>
+        <v>19840</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1018,87 +1029,50 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>26</v>
-      </c>
-      <c r="O6" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>139</v>
-      </c>
-      <c r="R6" t="n">
-        <v>39000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>144</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>26</v>
-      </c>
-      <c r="W6" t="n">
-        <v>176</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>208</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>52000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>11950000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>225</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.66666666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
+        <v>45584.375</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>83186</v>
+        <v>53331</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1123,87 +1097,50 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>28</v>
-      </c>
-      <c r="O7" t="n">
-        <v>185</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>171</v>
-      </c>
-      <c r="R7" t="n">
-        <v>380000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>94500000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>175</v>
-      </c>
-      <c r="U7" t="n">
-        <v>8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>29</v>
-      </c>
-      <c r="W7" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>316</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>181000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>73000000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>319</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.375</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pulido j 
-  esp </t>
-        </is>
-      </c>
+        <v>45584.46875</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14624</v>
+        <v>23516</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1228,87 +1165,50 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>180.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>368</v>
-      </c>
-      <c r="R8" t="n">
-        <v>210000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>63900000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>399</v>
-      </c>
-      <c r="U8" t="n">
-        <v>10</v>
-      </c>
-      <c r="V8" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="W8" t="n">
-        <v>186.3333333333333</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>244</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>96000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>102000000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>254</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.46875</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
+        <v>45584.5625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19840</v>
+        <v>14624</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1341,63 +1241,42 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="W9" t="n">
-        <v>182.3333333333333</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>255</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>405000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>158000000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>264</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>11</v>
-      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.5625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
+        <v>45584.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>42714</v>
+        <v>24791</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1422,87 +1301,50 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>27</v>
-      </c>
-      <c r="O10" t="n">
-        <v>184</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>78</v>
-      </c>
-      <c r="R10" t="n">
-        <v>33000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>79</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>31.66666666666667</v>
-      </c>
-      <c r="W10" t="n">
-        <v>178.6666666666667</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>239</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>106000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>45500000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>239</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.66666666666</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diaz de mera i 
-  esp </t>
-        </is>
-      </c>
+        <v>45585.375</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40000</v>
+        <v>26020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1527,82 +1369,50 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>178.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>154</v>
-      </c>
-      <c r="R11" t="n">
-        <v>67000</v>
-      </c>
-      <c r="S11" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="T11" t="n">
-        <v>165</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>162</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>146000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>46500000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>165</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45583.66666666666</v>
+        <v>45585.46875</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>19840</v>
+        <v>70460</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1647,30 +1457,30 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.375</v>
+        <v>45585.5625</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53331</v>
+        <v>23000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1715,30 +1525,30 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45584.46875</v>
+        <v>45585.66666666666</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>23516</v>
+        <v>55926</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H14" t="n">

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -545,6 +625,38 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>177</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -597,6 +709,38 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>188</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>163</v>
+      </c>
+      <c r="R3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>71500000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>168</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,6 +793,54 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O4" t="n">
+        <v>179</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>29000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>32</v>
+      </c>
+      <c r="W4" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>162</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>78000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>162</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -701,6 +893,54 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>361</v>
+      </c>
+      <c r="R5" t="n">
+        <v>191000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>26900000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>391</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="W5" t="n">
+        <v>179</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>233</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>110000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>244</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -753,6 +993,54 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="n">
+        <v>180</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>225</v>
+      </c>
+      <c r="R6" t="n">
+        <v>81000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>18800000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>229</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="W6" t="n">
+        <v>181</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>640000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>141500000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>261</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -805,6 +1093,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -857,6 +1161,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -909,6 +1229,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -961,6 +1297,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1013,6 +1365,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1065,6 +1433,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1117,6 +1501,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1169,6 +1569,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1221,6 +1637,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1273,6 +1705,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1325,6 +1773,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1377,6 +1841,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1429,6 +1909,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1481,6 +1977,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1533,6 +2045,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -583,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45583.66666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio mendizorrotza
@@ -667,7 +672,12 @@
       <c r="B3" s="2" t="n">
         <v>45584.375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio san mames
@@ -751,7 +761,12 @@
       <c r="B4" s="2" t="n">
         <v>45584.46875</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio el sadar
@@ -793,30 +808,14 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>27</v>
-      </c>
-      <c r="O4" t="n">
-        <v>179</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>29000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
         <v>32</v>
       </c>
@@ -851,7 +850,12 @@
       <c r="B5" s="2" t="n">
         <v>45584.5625</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio municipal de montilivi
@@ -894,52 +898,52 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>27.6</v>
+        <v>26.14285714285714</v>
       </c>
       <c r="O5" t="n">
-        <v>178.2</v>
+        <v>179.7142857142857</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
-        <v>361</v>
+        <v>515</v>
       </c>
       <c r="R5" t="n">
-        <v>191000</v>
+        <v>255000</v>
       </c>
       <c r="S5" t="n">
-        <v>26900000</v>
+        <v>73700000</v>
       </c>
       <c r="T5" t="n">
-        <v>391</v>
+        <v>557</v>
       </c>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V5" t="n">
-        <v>27.66666666666667</v>
+        <v>32</v>
       </c>
       <c r="W5" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="Z5" t="n">
-        <v>110000</v>
+        <v>45000</v>
       </c>
       <c r="AA5" t="n">
-        <v>39000000</v>
+        <v>14500000</v>
       </c>
       <c r="AB5" t="n">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -951,7 +955,12 @@
       <c r="B6" s="2" t="n">
         <v>45584.66666666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de balaidos
@@ -994,52 +1003,52 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O6" t="n">
-        <v>180</v>
+        <v>181.5</v>
       </c>
       <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>153</v>
+      </c>
+      <c r="R6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15800000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>154</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>32</v>
+      </c>
+      <c r="W6" t="n">
+        <v>173</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>260000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>86</v>
+      </c>
+      <c r="AC6" t="n">
         <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>225</v>
-      </c>
-      <c r="R6" t="n">
-        <v>81000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>18800000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>229</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>29.33333333333333</v>
-      </c>
-      <c r="W6" t="n">
-        <v>181</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>257</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>640000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>141500000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>261</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -1051,7 +1060,12 @@
       <c r="B7" s="2" t="n">
         <v>45585.375</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">estadi mallorca son moix
@@ -1093,22 +1107,54 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="O7" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>222</v>
+      </c>
+      <c r="R7" t="n">
+        <v>82000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>27200000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>236</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>26</v>
+      </c>
+      <c r="W7" t="n">
+        <v>176</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>208</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>52000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>11950000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>225</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1119,7 +1165,12 @@
       <c r="B8" s="2" t="n">
         <v>45585.46875</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">metropolitano stadium
@@ -1187,7 +1238,12 @@
       <c r="B9" s="2" t="n">
         <v>45585.5625</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de la ceramica
@@ -1255,7 +1311,12 @@
       <c r="B10" s="2" t="n">
         <v>45585.66666666666</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">estadi olimpic lluis companys
@@ -1323,7 +1384,12 @@
       <c r="B11" s="2" t="n">
         <v>45586.66666666666</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de mestalla

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -503,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45590.66666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">rcde stadium
@@ -545,6 +630,38 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>182</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>147</v>
+      </c>
+      <c r="R2" t="n">
+        <v>34000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>154</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -555,7 +672,12 @@
       <c r="B3" s="2" t="n">
         <v>45591.375</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio jose zorrilla
@@ -596,6 +718,54 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N3" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="O3" t="n">
+        <v>183.6666666666667</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>209</v>
+      </c>
+      <c r="R3" t="n">
+        <v>56000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5025000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>215</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>30.66666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>471</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>247000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>82100000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>474</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -607,7 +777,12 @@
       <c r="B4" s="2" t="n">
         <v>45591.46875</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">campo de futbol de vallecas
@@ -648,6 +823,54 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O4" t="n">
+        <v>177</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>138</v>
+      </c>
+      <c r="R4" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10050000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>152</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>26</v>
+      </c>
+      <c r="W4" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>214</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>56000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>230</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -659,7 +882,12 @@
       <c r="B5" s="2" t="n">
         <v>45591.5625</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de gran canaria
@@ -700,6 +928,54 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N5" t="n">
+        <v>26</v>
+      </c>
+      <c r="O5" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>147</v>
+      </c>
+      <c r="R5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>152</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>733</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>355000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>99200000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>801</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +987,12 @@
       <c r="B6" s="2" t="n">
         <v>45591.66666666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio santiago bernabeu
@@ -752,6 +1033,54 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N6" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="O6" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>343</v>
+      </c>
+      <c r="R6" t="n">
+        <v>880000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>352</v>
+      </c>
+      <c r="U6" t="n">
+        <v>14</v>
+      </c>
+      <c r="V6" t="n">
+        <v>30</v>
+      </c>
+      <c r="W6" t="n">
+        <v>187</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>172</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>305000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>87500000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>174</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -763,7 +1092,12 @@
       <c r="B7" s="2" t="n">
         <v>45592.41666666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio municipal de butarque
@@ -804,6 +1138,54 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N7" t="n">
+        <v>22</v>
+      </c>
+      <c r="O7" t="n">
+        <v>180</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>64</v>
+      </c>
+      <c r="R7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>27</v>
+      </c>
+      <c r="W7" t="n">
+        <v>182</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>141</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>39000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>145</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -815,7 +1197,12 @@
       <c r="B8" s="2" t="n">
         <v>45592.51041666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">coliseum
@@ -856,6 +1243,54 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N8" t="n">
+        <v>27</v>
+      </c>
+      <c r="O8" t="n">
+        <v>182</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>79</v>
+      </c>
+      <c r="R8" t="n">
+        <v>42000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>80</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>383</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>179000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>79400000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>401</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -867,7 +1302,12 @@
       <c r="B9" s="2" t="n">
         <v>45592.60416666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio benito villamarin
@@ -908,6 +1348,54 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N9" t="n">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="O9" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>240</v>
+      </c>
+      <c r="R9" t="n">
+        <v>107000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>243</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="W9" t="n">
+        <v>183</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>314</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>269000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>327</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -919,7 +1407,12 @@
       <c r="B10" s="2" t="n">
         <v>45592.70833333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">reale arena
@@ -960,6 +1453,54 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N10" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>457</v>
+      </c>
+      <c r="R10" t="n">
+        <v>196000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>89200000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>488</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" t="n">
+        <v>27</v>
+      </c>
+      <c r="W10" t="n">
+        <v>179</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -971,7 +1512,12 @@
       <c r="B11" s="2" t="n">
         <v>45593.70833333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">estadi mallorca son moix
@@ -1013,526 +1559,22 @@
           <t>laliga</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45597.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>19840</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>148</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>23516</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>148</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.51041666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>14624</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>148</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.60416666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>148</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45598.70833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>49430</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>148</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45599.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>70460</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>148</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.51041666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>55926</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>148</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>148</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45599.70833333334</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>148</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45600.70833333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>148</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -545,6 +625,54 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>21</v>
+      </c>
+      <c r="O2" t="n">
+        <v>182</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>69</v>
+      </c>
+      <c r="R2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>79</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>23</v>
+      </c>
+      <c r="W2" t="n">
+        <v>183</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>82</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -597,6 +725,22 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,34 +793,82 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>730</v>
+      </c>
+      <c r="R4" t="n">
+        <v>305000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>115200000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>805</v>
+      </c>
+      <c r="U4" t="n">
+        <v>13</v>
+      </c>
+      <c r="V4" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="W4" t="n">
+        <v>186</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>215</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>78000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>11400000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>226</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YFePBifU</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45599.41666666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23000</v>
+        <v>70460</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -700,35 +892,83 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>318</v>
+      </c>
+      <c r="R5" t="n">
+        <v>255000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>84500000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>331</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="W5" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>223</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>68000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>23500000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>237</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zHmSVfun</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.70833333334</v>
+        <v>45599.51041666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49430</v>
+        <v>55926</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -752,35 +992,83 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="n">
+        <v>187</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>172</v>
+      </c>
+      <c r="R6" t="n">
+        <v>305000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>87500000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>174</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>217</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>47000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>231</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.41666666666</v>
+        <v>45599.60416666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70460</v>
+        <v>42714</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -804,35 +1092,83 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N7" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>153</v>
+      </c>
+      <c r="R7" t="n">
+        <v>45000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>21900000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>160</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>179</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>287</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>103000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>28400000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>323</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.51041666666</v>
+        <v>45599.70833333334</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55926</v>
+        <v>53331</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -856,35 +1192,83 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N8" t="n">
+        <v>27</v>
+      </c>
+      <c r="O8" t="n">
+        <v>190</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>86</v>
+      </c>
+      <c r="R8" t="n">
+        <v>39000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>87</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>30.33333333333333</v>
+      </c>
+      <c r="W8" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>240</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>107000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>243</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.60416666666</v>
+        <v>45600.70833333334</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42714</v>
+        <v>24791</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -909,630 +1293,22 @@
           <t>laliga</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45599.70833333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>53331</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>148</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45600.70833333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>24791</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>148</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rPc4X7Gj</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45604.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>14708</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>148</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nucZxUhT</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>83186</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>148</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bXuieB8c</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.51041666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>23000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>lUatW5jE</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>148</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jFGHcfig</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>148</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>CMriQj9N</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>148</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>60721</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>148</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Ia5ItCg4</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.51041666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>26020</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>148</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UwPNKUWp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>12454</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>148</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45606.60416666666</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>148</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QP8QvjOG</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45606.70833333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>148</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,114 +493,34 @@
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45604.70833333334</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19840</v>
+        <v>14708</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -624,83 +544,35 @@
         <is>
           <t>laliga</t>
         </is>
-      </c>
-      <c r="N2" t="n">
-        <v>21</v>
-      </c>
-      <c r="O2" t="n">
-        <v>182</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>69</v>
-      </c>
-      <c r="R2" t="n">
-        <v>14000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>79</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>23</v>
-      </c>
-      <c r="W2" t="n">
-        <v>183</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>74</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>21000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>82</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.41666666666</v>
+        <v>45605.41666666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23516</v>
+        <v>83186</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -725,50 +597,34 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.51041666666</v>
+        <v>45605.51041666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14624</v>
+        <v>23000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -792,83 +648,35 @@
         <is>
           <t>laliga</t>
         </is>
-      </c>
-      <c r="N4" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="O4" t="n">
-        <v>179.2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>730</v>
-      </c>
-      <c r="R4" t="n">
-        <v>305000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>115200000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>805</v>
-      </c>
-      <c r="U4" t="n">
-        <v>13</v>
-      </c>
-      <c r="V4" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="W4" t="n">
-        <v>186</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>215</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>78000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>11400000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>226</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.41666666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">metropolitano stadium
-  madrid </t>
+          <t xml:space="preserve">rcde stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70460</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -892,83 +700,35 @@
         <is>
           <t>laliga</t>
         </is>
-      </c>
-      <c r="N5" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>179.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>318</v>
-      </c>
-      <c r="R5" t="n">
-        <v>255000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>84500000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>331</v>
-      </c>
-      <c r="U5" t="n">
-        <v>10</v>
-      </c>
-      <c r="V5" t="n">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="W5" t="n">
-        <v>179.6666666666667</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>223</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>68000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>23500000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>237</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45599.51041666666</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>55926</v>
+        <v>12454</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -992,83 +752,35 @@
         <is>
           <t>laliga</t>
         </is>
-      </c>
-      <c r="N6" t="n">
-        <v>30</v>
-      </c>
-      <c r="O6" t="n">
-        <v>187</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>172</v>
-      </c>
-      <c r="R6" t="n">
-        <v>305000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>87500000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>174</v>
-      </c>
-      <c r="U6" t="n">
-        <v>8</v>
-      </c>
-      <c r="V6" t="n">
-        <v>25</v>
-      </c>
-      <c r="W6" t="n">
-        <v>180.3333333333333</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>217</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>47000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>231</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.60416666666</v>
+        <v>45606.41666666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
+          <t xml:space="preserve">estadio benito villamarin
   sevilla </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42714</v>
+        <v>60721</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1092,83 +804,35 @@
         <is>
           <t>laliga</t>
         </is>
-      </c>
-      <c r="N7" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>191.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>153</v>
-      </c>
-      <c r="R7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>21900000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>160</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="W7" t="n">
-        <v>179</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>287</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>103000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>28400000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>323</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.70833333334</v>
+        <v>45606.51041666666</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53331</v>
+        <v>26020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1192,83 +856,35 @@
         <is>
           <t>laliga</t>
         </is>
-      </c>
-      <c r="N8" t="n">
-        <v>27</v>
-      </c>
-      <c r="O8" t="n">
-        <v>190</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>86</v>
-      </c>
-      <c r="R8" t="n">
-        <v>39000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>87</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>30.33333333333333</v>
-      </c>
-      <c r="W8" t="n">
-        <v>182.3333333333333</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>240</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>107000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>54000000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>243</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45600.70833333334</v>
+        <v>45606.60416666666</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24791</v>
+        <v>16500</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1293,22 +909,110 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>27618</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>148</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45606.70833333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>148</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -503,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45604.70833333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">campo de futbol de vallecas
@@ -544,6 +629,54 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N2" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="O2" t="n">
+        <v>176.6666666666667</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>222</v>
+      </c>
+      <c r="R2" t="n">
+        <v>64000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>228</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>178.6666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>223</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>68000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>23500000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>237</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +688,12 @@
       <c r="B3" s="2" t="n">
         <v>45605.41666666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio santiago bernabeu
@@ -597,6 +735,38 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>29</v>
+      </c>
+      <c r="O3" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>433</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1220000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>327500000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>441</v>
+      </c>
+      <c r="U3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -607,7 +777,12 @@
       <c r="B4" s="2" t="n">
         <v>45605.51041666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">estadio de la ceramica
@@ -648,35 +823,88 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N4" t="n">
+        <v>28.66666666666667</v>
+      </c>
+      <c r="O4" t="n">
+        <v>183</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>241</v>
+      </c>
+      <c r="R4" t="n">
+        <v>147000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>67500000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>244</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>140</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>34000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>153</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>12454</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -700,35 +928,88 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>285</v>
+      </c>
+      <c r="R5" t="n">
+        <v>107000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>306</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" t="n">
+        <v>26.83333333333333</v>
+      </c>
+      <c r="W5" t="n">
+        <v>182.1666666666667</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>447</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>188000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>65600000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>475</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45606.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12454</v>
+        <v>60721</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -752,35 +1033,88 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N6" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>381</v>
+      </c>
+      <c r="R6" t="n">
+        <v>146000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75525000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>390</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="W6" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>210</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>54000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>223</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45606.41666666666</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45606.51041666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60721</v>
+        <v>26020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -804,35 +1138,88 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>52000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15600000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>155</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>163</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>153000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>166</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45606.51041666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26020</v>
+        <v>16500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -856,35 +1243,88 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N8" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>181</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>226</v>
+      </c>
+      <c r="R8" t="n">
+        <v>93000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>30800000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>236</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>22.83333333333333</v>
+      </c>
+      <c r="W8" t="n">
+        <v>177.1666666666667</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>423</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>111000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>31900000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>477</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>45606.60416666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16500</v>
+        <v>27618</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -909,34 +1349,55 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45606.60416666666</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45606.70833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>27618</v>
+        <v>40000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -960,35 +1421,83 @@
         <is>
           <t>laliga</t>
         </is>
+      </c>
+      <c r="N10" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>179</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>287</v>
+      </c>
+      <c r="R10" t="n">
+        <v>103000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>28400000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>323</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>185</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>402</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>522000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>144000000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>430</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45606.70833333334</v>
+        <v>45618.70833333334</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>40000</v>
+        <v>16500</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1013,6 +1522,294 @@
           <t>laliga</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.41666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>148</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.51041666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>70460</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>148</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>14624</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>148</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>32392</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>148</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
